--- a/data/monthly/2026-07_월별취합.xlsx
+++ b/data/monthly/2026-07_월별취합.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="브랜드통계" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="월별요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="카카오선물하기" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="다이소몰" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="브랜드통계" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23일</t>
+          <t>25일</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>43,249원</t>
+          <t>43,266원</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3,375원</t>
+          <t>3,275원</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,957원</t>
+          <t>19,779원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30개</t>
+          <t>31개</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35,203원</t>
+          <t>35,230원</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
         <v>3.4</v>
       </c>
       <c r="C19" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="D19" t="n">
         <v>13</v>
@@ -739,7 +739,7 @@
         <v>1.7</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -898,21 +898,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>카카오선물하기</t>
+          <t>다이소몰</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
         <v>14</v>
@@ -921,24 +921,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>다이소몰</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>마그네슘 30정 30일분</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30"/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1016,79 +1016,79 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>카카오선물하기</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>카카오선물하기</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>다이소몰</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38"/>
@@ -1131,10 +1131,10 @@
         <v>28.3</v>
       </c>
       <c r="C41" t="n">
-        <v>41.7</v>
+        <v>45</v>
       </c>
       <c r="D41" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="42">
@@ -1188,17 +1188,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="46"/>
@@ -1241,10 +1241,10 @@
         <v>21.7</v>
       </c>
       <c r="C49" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="D49" t="n">
-        <v>-5</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="50">
@@ -1298,7 +1298,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1315,7 +1315,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>신규 진입 상품 (49개)</t>
+          <t>신규 진입 상품 (48개)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+손풍기+레드파로효소캡슐레이션+파로저당견과류바+파로차진액스틱14포</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+손풍기+레드파로효소캡슐레이션+파로저당견과류바+파로차진액스틱14포</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
+          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
@@ -1569,16 +1569,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
@@ -1589,16 +1589,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>바나바잎 10정 10일분</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>이너케어＆유산균 30캡슐</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000 10포</t>
+          <t>이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -1969,16 +1969,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
@@ -1989,16 +1989,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
+          <t>[7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>슬리플러스</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
+          <t>식물성 멜라토닌 함유 멜라메이트 구미/로우슈가 구미 (20/50구미)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>슬리플러스</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2109,16 +2109,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[7월 올영픽/1일1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -2129,16 +2129,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>라이필</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미</t>
+          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 코자아 식물성 멜라토닌 함유 젤리 기획 (+10구미+틴케이스) (20일분)</t>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>온리추얼 리셋 브이라인 7포 (+1포 증정) (8일분)</t>
+          <t>[1+1]알디콤 속쓰헤소제 4포입 3종(플러스,에이,브이)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2269,16 +2269,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 속쓰헤소제 4포입 3종(플러스,에이,브이)</t>
+          <t>온리추얼 리셋 브이라인 7포 (+1포 증정) (8일분)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
@@ -2298,56 +2298,58 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="106"/>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>신제품 기획 인사이트 (급성장·특이사항 재해석)</t>
+        </is>
+      </c>
+    </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>신제품 기획 인사이트 (급성장·특이사항 재해석)</t>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>핵심수치</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>신제품 시사점</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>핵심수치</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>신제품 시사점</t>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>급성장 카테고리</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>28.3%→45.0% (+16.7%p)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>'기타/특수목적' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2359,17 +2361,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>28.3%→41.7% (+13.4%p)</t>
+          <t>18.3%→21.7% (+3.4%p)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>'기타/특수목적' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>'다이어트/체중관리' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2381,17 +2383,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>18.3%→21.7% (+3.4%p)</t>
+          <t>0.0%→1.7% (+1.7%p)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>'다이어트/체중관리' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>'홍삼/인삼' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2405,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.0%→1.7% (+1.7%p)</t>
+          <t>1.7%→3.3% (+1.6%p)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>'홍삼/인삼' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>'혈행' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2425,39 +2427,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1.7%→3.3% (+1.6%p)</t>
+          <t>5.0%→3.3% (-1.7%p)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>'혈행' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>'피부/미용' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>급성장 카테고리</t>
+          <t>급성장 제품</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>[다이소몰] 셀트리온 - [다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5.0%→5.0% (+0.0%p)</t>
+          <t>13위 → 1위</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>'루테인/눈건강' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
         </is>
       </c>
     </row>
@@ -2469,12 +2471,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[다이소몰] 셀트리온 - [다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>[카카오선물하기] 한끼통살 - [한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>13위 → 1위</t>
+          <t>11위 → 5위</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2491,12 +2493,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 한끼통살 - [한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>[올리브영] 프로뉴트리션 - 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>11위 → 5위</t>
+          <t>6위 → 1위</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2513,12 +2515,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[올리브영] 프로뉴트리션 - 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[다이소몰] 대웅제약 - 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>6위 → 1위</t>
+          <t>17위 → 14위</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2535,12 +2537,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 한끼통살 - [한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>[올리브영] 고려은단 - 고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>18위 → 14위</t>
+          <t>9위 → 6위</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2552,22 +2554,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>급성장 제품</t>
+          <t>신규 진입(특이사항 후보)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[다이소몰] 대웅제약 - 마그네슘 30정 30일분</t>
+          <t>[카카오선물하기] 옵티젠 - 한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>17위 → 14위</t>
+          <t>이번 달 1위 신규 진입</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
+          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2581,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 옵티젠 - 한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>[카카오선물하기] 그레인온 - [그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+파인키위효소 증정</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>이번 달 1위 신규 진입</t>
+          <t>이번 달 2위 신규 진입</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2601,7 +2603,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 그레인온 - [그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+파인키위효소 증정</t>
+          <t>[다이소몰] 동국제약 - [신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2623,7 +2625,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[다이소몰] 동국제약 - [신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>[올리브영] 리쥬란 - [7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2645,37 +2647,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[올리브영] 슬리플러스 - [올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
+          <t>[다이소몰] 종근당 - 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>이번 달 2위 신규 진입</t>
+          <t>이번 달 3위 신규 진입</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
-        <is>
-          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>신규 진입(특이사항 후보)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>[올리브영] 리쥬란 - [7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>이번 달 3위 신규 진입</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
         <is>
           <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
         </is>
@@ -2809,7 +2789,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2870,7 +2850,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2903,7 +2883,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2917,7 +2897,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2950,7 +2930,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2974,7 +2954,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47,473원</t>
+          <t>47,348원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2984,11 +2964,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>▼27원</t>
+          <t>▼152원</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
@@ -2999,7 +2979,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -3046,7 +3026,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -3055,22 +3035,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+손풍기+레드파로효소캡슐레이션+파로저당견과류바+파로차진액스틱14포</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44,684원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3084,7 +3064,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
@@ -3093,7 +3073,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3107,7 +3087,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3117,7 +3097,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34,000원</t>
+          <t>44,523원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3131,7 +3111,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
@@ -3140,7 +3120,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -3149,22 +3129,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+손풍기+레드파로효소캡슐레이션+파로저당견과류바+파로차진액스틱14포</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>34,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3211,7 +3191,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>63,584원</t>
+          <t>63,804원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3225,7 +3205,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.11</v>
+        <v>4.38</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -3234,7 +3214,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -3290,27 +3270,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>54,833원</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3319,18 +3299,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>▼4</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3339,27 +3317,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
+          <t>옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3368,16 +3346,18 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼5</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -3386,47 +3366,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35,753원</t>
+          <t>62,000원</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42,866원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>▼7,113원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>18</v>
-      </c>
+        <v>2.71</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>▲4</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -3464,7 +3442,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.26</v>
+        <v>5.38</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
@@ -3473,7 +3451,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3487,7 +3465,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인애플키위효소(1개월) +파로저당견과류바</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3497,7 +3475,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>54,420원</t>
+          <t>42,233원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3511,7 +3489,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
@@ -3520,7 +3498,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3529,45 +3507,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인애플키위효소(1개월) +파로저당견과류바</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42,233원</t>
+          <t>35,753원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42,866원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼7,113원</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>18</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▲1</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3623,22 +3603,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43,000원</t>
+          <t>35,190원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3652,7 +3632,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>5.95</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
@@ -3661,7 +3641,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -3670,22 +3650,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35,210원</t>
+          <t>43,000원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3699,7 +3679,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
@@ -3708,7 +3688,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3830,7 +3810,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
@@ -3841,7 +3821,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3879,7 +3859,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -3888,7 +3868,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3897,27 +3877,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3926,14 +3906,12 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
+        <v>3.67</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>▼1</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -3946,22 +3924,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>루테인 30정 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3993,22 +3971,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>루테인 30정 30일분</t>
+          <t>푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4022,7 +4000,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -4031,7 +4009,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4040,22 +4018,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>푸응 7days 팻버닝 21캡슐</t>
+          <t>바나바잎 추출물 30정 (30일분)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4069,7 +4047,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -4078,7 +4056,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4087,27 +4065,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>바나바잎 추출물 30정 (30일분)</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4116,16 +4094,18 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼5</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4134,22 +4114,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4163,7 +4143,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.09</v>
+        <v>4.67</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
@@ -4172,7 +4152,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4181,22 +4161,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>바나바잎 10정 10일분</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4233,17 +4213,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4257,7 +4237,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.67</v>
+        <v>6.25</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -4266,7 +4246,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -4465,22 +4445,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4494,7 +4474,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
@@ -4503,7 +4483,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -4512,22 +4492,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>이너케어＆유산균 30캡슐</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4541,7 +4521,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
@@ -4550,7 +4530,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -4559,17 +4539,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000 10포</t>
+          <t>이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4588,7 +4568,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6.17</v>
+        <v>5.33</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
@@ -4597,7 +4577,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -4606,17 +4586,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4626,7 +4606,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4635,18 +4615,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="I19" t="n">
-        <v>5</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>▼13</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -4655,22 +4633,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4684,7 +4662,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
@@ -4693,7 +4671,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -4707,12 +4685,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4722,7 +4700,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4731,16 +4709,18 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼10</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4758,7 +4738,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -4848,7 +4828,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35,203원</t>
+          <t>35,230원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4858,11 +4838,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>▼108원</t>
+          <t>▼81원</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -4873,7 +4853,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4887,17 +4867,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
+          <t>[7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>슬리플러스</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4934,17 +4914,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
+          <t>식물성 멜라토닌 함유 멜라메이트 구미/로우슈가 구미 (20/50구미)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>8,900원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4981,17 +4961,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>슬리플러스</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27,806원</t>
+          <t>15,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5005,7 +4985,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.31</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -5014,7 +4994,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5028,17 +5008,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12,957원</t>
+          <t>27,706원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5052,7 +5032,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5.07</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -5061,7 +5041,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -5070,47 +5050,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21,325원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29,006원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>▼7,681원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>▼2</t>
+          <t>▲3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5119,45 +5099,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18,223원</t>
+          <t>21,325원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29,006원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼7,681원</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -5166,22 +5148,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14,960원</t>
+          <t>18,223원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5195,7 +5177,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>5.08</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
@@ -5204,7 +5186,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -5260,22 +5242,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미</t>
+          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>라이필</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>14,960원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5289,7 +5271,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -5307,27 +5289,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>14,587원</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5336,18 +5318,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
+        <v>4.88</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>▼2</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -5356,22 +5336,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17,057원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5385,7 +5365,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.71</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -5394,7 +5374,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5450,22 +5430,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 코자아 식물성 멜라토닌 함유 젤리 기획 (+10구미+틴케이스) (20일분)</t>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27,800원</t>
+          <t>17,057원</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5479,7 +5459,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>6.71</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
@@ -5488,7 +5468,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -5526,7 +5506,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
@@ -5535,7 +5515,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -5549,17 +5529,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>온리추얼 리셋 브이라인 7포 (+1포 증정) (8일분)</t>
+          <t>[1+1]알디콤 속쓰헤소제 4포입 3종(플러스,에이,브이)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>15,435원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5591,41 +5571,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 속쓰헤소제 4포입 3종(플러스,에이,브이)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15,435원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲5,000원</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼16</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -5638,12 +5620,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+          <t>온리추얼 리셋 브이라인 7포 (+1포 증정) (8일분)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5653,28 +5635,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>▲5,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>▼17</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -5692,36 +5672,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[7월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포) (14일분)</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17,700원</t>
+          <t>9,700원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10,534원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼834원</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>5.5</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>11</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼8</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -5734,22 +5716,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
+          <t>[7월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포) (14일분)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>17,700원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5763,7 +5745,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
@@ -5772,7 +5754,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5848,16 +5830,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>21.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-5</v>
+        <v>-6.7</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -5866,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5960,22 +5942,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6128,25 +6110,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>41.7</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
         <v>28.3</v>
       </c>
       <c r="E12" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -6186,7 +6168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6248,22 +6230,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6272,20 +6254,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
         <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -6294,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6310,10 +6292,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -6380,35 +6362,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-3</v>
-      </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6418,16 +6400,16 @@
         <v>3.3</v>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6436,7 +6418,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6445,8 +6427,12 @@
       <c r="C9" t="n">
         <v>3.3</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -6484,7 +6470,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6494,10 +6480,10 @@
         <v>3.3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6512,7 +6498,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6522,10 +6508,10 @@
         <v>3.3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6540,63 +6526,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6605,12 +6591,8 @@
       <c r="C15" t="n">
         <v>1.7</v>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>1</v>
       </c>
@@ -6624,7 +6606,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6640,10 +6622,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -6652,7 +6634,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6664,10 +6646,10 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6676,7 +6658,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6685,12 +6667,8 @@
       <c r="C18" t="n">
         <v>1.7</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>0</v>
       </c>
@@ -6704,7 +6682,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6728,7 +6706,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6780,7 +6758,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6789,22 +6767,26 @@
       <c r="C22" t="n">
         <v>1.7</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6813,12 +6795,8 @@
       <c r="C23" t="n">
         <v>1.7</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
         <v>0</v>
       </c>
@@ -6856,7 +6834,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6865,8 +6843,12 @@
       <c r="C25" t="n">
         <v>1.7</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5</v>
+      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
@@ -6880,7 +6862,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6908,7 +6890,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>라이필</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6918,10 +6900,10 @@
         <v>1.7</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -7012,7 +6994,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7021,8 +7003,12 @@
       <c r="C31" t="n">
         <v>1.7</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
@@ -7030,6 +7016,30 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>대원제약</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/monthly/2026-07_월별취합.xlsx
+++ b/data/monthly/2026-07_월별취합.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="월별요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="카카오선물하기" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="다이소몰" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="브랜드통계" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="브랜드통계" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>43,266원</t>
+          <t>40,100원</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3,275원</t>
+          <t>3,075원</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,779원</t>
+          <t>22,615원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31개</t>
+          <t>36개</t>
         </is>
       </c>
     </row>
@@ -580,12 +580,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>34,000원</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35,230원</t>
+          <t>35,124원</t>
         </is>
       </c>
     </row>
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="C19" t="n">
-        <v>4.75</v>
+        <v>5.34</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.7</v>
       </c>
       <c r="C20" t="n">
-        <v>5.95</v>
+        <v>6.12</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -770,14 +770,14 @@
         <v>1.6</v>
       </c>
       <c r="C21" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>코엔자임Q10 6캡슐 6일분</t>
+          <t>코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -866,10 +866,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -880,65 +880,65 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>다이소몰</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>마그네슘 30정 30일분</t>
+          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>카카오선물하기</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30"/>
@@ -984,19 +984,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1019,7 +1019,7 @@
         <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
@@ -1030,65 +1030,65 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>카카오선물하기</t>
+          <t>다이소몰</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>다이소몰</t>
+          <t>카카오선물하기</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38"/>
@@ -1131,10 +1131,10 @@
         <v>28.3</v>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>38.3</v>
       </c>
       <c r="D41" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -1147,10 +1147,10 @@
         <v>18.3</v>
       </c>
       <c r="C42" t="n">
-        <v>21.7</v>
+        <v>26.7</v>
       </c>
       <c r="D42" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="43">
@@ -1195,10 +1195,10 @@
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46"/>
@@ -1241,10 +1241,10 @@
         <v>21.7</v>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="D49" t="n">
-        <v>-6.7</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="50">
@@ -1266,46 +1266,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="D51" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="C52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.3</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C53" t="n">
         <v>5</v>
-      </c>
-      <c r="C53" t="n">
-        <v>3.3</v>
       </c>
       <c r="D53" t="n">
         <v>-1.7</v>
@@ -1315,7 +1315,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>신규 진입 상품 (48개)</t>
+          <t>신규 진입 상품 (51개)</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1429,16 +1429,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+손풍기+레드파로효소캡슐레이션+파로저당견과류바+파로차진액스틱14포</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1509,16 +1509,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -1529,16 +1529,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
@@ -1549,16 +1549,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>[카사베르디] 유기농 레드와인 비니거 스틱 3박스(총42포)+리센느포토카드&amp;포스터+추가사은품 증정</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인애플키위효소(1개월) +파로저당견과류바</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -1629,16 +1629,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72">
@@ -1649,16 +1649,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>센트룸</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
@@ -1669,36 +1669,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>다이소몰</t>
+          <t>카카오선물하기</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
@@ -1709,16 +1709,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>루테인 30정 30일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>푸응 7days 팻버닝 21캡슐</t>
+          <t>데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>바나바잎 추출물 30정 (30일분)</t>
+          <t>루테인 30정 30일분</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1789,16 +1789,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>바나바잎 10정 10일분</t>
+          <t>리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -1809,16 +1809,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -1829,16 +1829,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>rTG 오메가3 30캡슐 30일분</t>
+          <t>코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -1869,16 +1869,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>코엔자임Q10 6캡슐 6일분</t>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
@@ -1889,16 +1889,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>코엔자임 Q10 30캡슐 30일분</t>
+          <t>이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -1909,16 +1909,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>녹차 카테킨 6정 6일분</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -1929,16 +1929,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>바나바잎 추출물 30정 (30일분)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -1949,16 +1949,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>이너케어＆유산균 30캡슐</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -1969,16 +1969,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000 10포</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89">
@@ -1989,56 +1989,56 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>다이어트 홀릭 15일분</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>다이소몰</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>다이소몰</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>식물성 멜라토닌 함유 멜라메이트 구미/로우슈가 구미 (20/50구미)</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -2049,16 +2049,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
+          <t>[7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>슬리플러스</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2069,16 +2069,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[올영단독/온열안대증정] 슬리플러스X카카오프렌즈 슬리핑보틀 100ml (1개입 /4개입 기획/6개입)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>슬리플러스</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -2089,16 +2089,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
+          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -2109,16 +2109,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2129,16 +2129,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -2149,16 +2149,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>CJ 바이오코어 비피더스 다이어트 유산균 14캡슐 (2주분)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -2169,16 +2169,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미</t>
+          <t>[7월 올영픽] 판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
@@ -2189,16 +2189,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[윤광UP]온리추얼 글로우업 글루타치온 콜라겐 7포 (+1포 증정)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
@@ -2209,16 +2209,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+          <t>[7월 올영픽] 코자아 식물성 멜라토닌 함유 젤리 기획 (+10구미+틴케이스) (20일분)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -2229,16 +2229,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CJ 바이오코어 비피더스 다이어트 유산균 14캡슐 (2주분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
@@ -2249,16 +2249,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 속쓰헤소제 4포입 3종(플러스,에이,브이)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
@@ -2269,16 +2269,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>온리추얼 리셋 브이라인 7포 (+1포 증정) (8일분)</t>
+          <t>[골라담기] 닥터언 매일루틴 이너헬스 8종 택 1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>닥터언</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
@@ -2289,111 +2289,105 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[7월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포) (14일분)</t>
+          <t>올더베러 웰니스 구미 30일분 6종 택1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="105"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>[추성훈PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>헬스헬퍼</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>17</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>[7월 올영픽] 오니스트 트리플콜라겐 오렌지 14일 루틴</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>오니스트</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
         <is>
           <t>신제품 기획 인사이트 (급성장·특이사항 재해석)</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
+      <c r="B110" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>핵심수치</t>
         </is>
       </c>
-      <c r="D107" s="1" t="inlineStr">
+      <c r="D110" s="1" t="inlineStr">
         <is>
           <t>신제품 시사점</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>급성장 카테고리</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>28.3%→45.0% (+16.7%p)</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>'기타/특수목적' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>급성장 카테고리</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>18.3%→21.7% (+3.4%p)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>'다이어트/체중관리' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>급성장 카테고리</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.0%→1.7% (+1.7%p)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>'홍삼/인삼' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2405,17 +2399,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1.7%→3.3% (+1.6%p)</t>
+          <t>28.3%→38.3% (+10.0%p)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>'혈행' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>'기타/특수목적' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2427,83 +2421,83 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>5.0%→3.3% (-1.7%p)</t>
+          <t>18.3%→26.7% (+8.4%p)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>'피부/미용' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
+          <t>'다이어트/체중관리' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>급성장 제품</t>
+          <t>급성장 카테고리</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[다이소몰] 셀트리온 - [다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>13위 → 1위</t>
+          <t>0.0%→1.7% (+1.7%p)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
+          <t>'홍삼/인삼' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>급성장 제품</t>
+          <t>급성장 카테고리</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 한끼통살 - [한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>11위 → 5위</t>
+          <t>1.7%→3.3% (+1.6%p)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
+          <t>'혈행' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>급성장 제품</t>
+          <t>급성장 카테고리</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[올리브영] 프로뉴트리션 - 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>6위 → 1위</t>
+          <t>5.0%→5.0% (+0.0%p)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
+          <t>'피부/미용' 수요 확대 — 관련 원료·제형 신제품 검토 우선순위로</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2509,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[다이소몰] 대웅제약 - 마그네슘 30정 30일분</t>
+          <t>[다이소몰] 셀트리온 - [다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>17위 → 14위</t>
+          <t>13위 → 1위</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2537,12 +2531,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[올리브영] 고려은단 - 고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[카카오선물하기] 한끼통살 - [한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>9위 → 6위</t>
+          <t>18위 → 10위</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2554,66 +2548,66 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>신규 진입(특이사항 후보)</t>
+          <t>급성장 제품</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 옵티젠 - 한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>[올리브영] 고려은단 - 고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>이번 달 1위 신규 진입</t>
+          <t>9위 → 3위</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
+          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>신규 진입(특이사항 후보)</t>
+          <t>급성장 제품</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[카카오선물하기] 그레인온 - [그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+파인키위효소 증정</t>
+          <t>[올리브영] 프로뉴트리션 - 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>이번 달 2위 신규 진입</t>
+          <t>6위 → 1위</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
+          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>신규 진입(특이사항 후보)</t>
+          <t>급성장 제품</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[다이소몰] 동국제약 - [신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>[카카오선물하기] 한끼통살 - [한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>이번 달 2위 신규 진입</t>
+          <t>11위 → 8위</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
+          <t>가격·구성·마케팅 포인트 벤치마킹 대상</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2619,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[올리브영] 리쥬란 - [7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
+          <t>[카카오선물하기] 오쏘몰 - 독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>이번 달 2위 신규 진입</t>
+          <t>이번 달 1위 신규 진입</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2647,15 +2641,81 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[다이소몰] 종근당 - 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>[카카오선물하기] 그레인온 - [그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+파인키위효소 증정</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>이번 달 2위 신규 진입</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>신규 진입(특이사항 후보)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>[다이소몰] 홀베리 - 홀베리 레몬 비타C 500 10개입</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>이번 달 2위 신규 진입</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>신규 진입(특이사항 후보)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>[올리브영] 리쥬란 - [7월 올영픽] 리쥬란 이너닷 DNA 글로우 젤리 14포 기획 (+1포) (15일분)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>이번 달 2위 신규 진입</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>신규 진입(특이사항 후보)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>[다이소몰] 동국제약 - [신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
           <t>이번 달 3위 신규 진입</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>신제형·신규 구성 여부 확인 후 벤치마킹 대상 추가 검토</t>
         </is>
@@ -2756,17 +2816,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>34,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2780,7 +2840,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -2789,7 +2849,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2813,7 +2873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44,650원</t>
+          <t>43,780원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2827,7 +2887,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -2836,7 +2896,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2850,17 +2910,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>34,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2874,7 +2934,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -2883,7 +2943,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -2897,7 +2957,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2907,7 +2967,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34,000원</t>
+          <t>109,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2921,7 +2981,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -2930,7 +2990,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -2939,47 +2999,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47,348원</t>
+          <t>54,833원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47,500원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>▼152원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>▲6</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2988,22 +3046,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>109,000원</t>
+          <t>62,870원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3017,7 +3075,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -3026,7 +3084,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3035,22 +3093,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+손풍기+레드파로효소캡슐레이션+파로저당견과류바+파로차진액스틱14포</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>44,280원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3064,7 +3122,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3.84</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
@@ -3073,7 +3131,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -3082,45 +3140,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44,523원</t>
+          <t>47,348원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47,500원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼152원</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>3.96</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▲3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -3129,22 +3189,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34,000원</t>
+          <t>63,820원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3158,7 +3218,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4.12</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
@@ -3167,7 +3227,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -3176,45 +3236,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>63,804원</t>
+          <t>35,173원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42,866원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼7,693원</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>4.74</v>
+      </c>
+      <c r="I11" t="n">
+        <v>18</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▲8</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -3228,7 +3290,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3238,7 +3300,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>21,500원</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3252,7 +3314,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.5</v>
+        <v>5.29</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
@@ -3261,7 +3323,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -3270,22 +3332,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54,833원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3299,7 +3361,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>5.32</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -3308,7 +3370,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -3317,27 +3379,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>21,481원</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3346,18 +3408,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>▼5</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -3366,22 +3426,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62,000원</t>
+          <t>35,160원</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3395,7 +3455,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.71</v>
+        <v>6.12</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
@@ -3404,7 +3464,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -3413,22 +3473,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>[카사베르디] 유기농 레드와인 비니거 스틱 3박스(총42포)+리센느포토카드&amp;포스터+추가사은품 증정</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>36,300원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3442,7 +3502,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.38</v>
+        <v>7.33</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
@@ -3451,7 +3511,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3460,22 +3520,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인애플키위효소(1개월) +파로저당견과류바</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42,233원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3489,7 +3549,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.33</v>
+        <v>6.52</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
@@ -3498,7 +3558,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -3512,42 +3572,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35,753원</t>
+          <t>26,455원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42,866원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>▼7,113원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I18" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>18</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>▲1</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -3556,22 +3614,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>센트룸</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21,481원</t>
+          <t>24,000원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3585,7 +3643,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>6.68</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
@@ -3594,7 +3652,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -3603,22 +3661,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35,190원</t>
+          <t>23,800원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3632,7 +3690,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.95</v>
+        <v>9</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
@@ -3641,7 +3699,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -3650,22 +3708,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43,000원</t>
+          <t>26,400원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3679,7 +3737,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>8.25</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
@@ -3688,7 +3746,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3835,17 +3893,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3859,7 +3917,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.43</v>
+        <v>1.67</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -3868,7 +3926,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3877,17 +3935,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3906,7 +3964,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -3915,7 +3973,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -3924,27 +3982,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>루테인 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3953,16 +4011,18 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼2</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3971,22 +4031,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>푸응 7days 팻버닝 21캡슐</t>
+          <t>데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4000,7 +4060,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -4009,7 +4069,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4018,12 +4078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>바나바잎 추출물 30정 (30일분)</t>
+          <t>루테인 30정 30일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4047,7 +4107,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>3.67</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -4056,7 +4116,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4065,17 +4125,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4085,7 +4145,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4094,18 +4154,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>▼5</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4161,17 +4219,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4190,7 +4248,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
@@ -4199,7 +4257,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -4208,22 +4266,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4237,7 +4295,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -4246,7 +4304,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -4255,17 +4313,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rTG 오메가3 30캡슐 30일분</t>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4284,7 +4342,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6.18</v>
+        <v>5.33</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
@@ -4293,7 +4351,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4302,22 +4360,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>코엔자임Q10 6캡슐 6일분</t>
+          <t>이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4331,7 +4389,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -4340,7 +4398,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4349,12 +4407,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>코엔자임 Q10 30캡슐 30일분</t>
+          <t>녹차 카테킨 6정 6일분</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4364,7 +4422,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4378,7 +4436,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -4387,7 +4445,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -4396,12 +4454,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>마그네슘 30정 30일분</t>
+          <t>바나바잎 추출물 30정 (30일분)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4416,7 +4474,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4425,18 +4483,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>17</v>
-      </c>
+        <v>5.56</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>▲3</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -4492,12 +4548,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4530,7 +4586,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -4539,17 +4595,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>이너케어＆유산균 30캡슐</t>
+          <t>다이어트 홀릭 15일분</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4568,7 +4624,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
@@ -4591,12 +4647,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000 10포</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4615,7 +4671,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
@@ -4624,7 +4680,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -4633,12 +4689,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4653,7 +4709,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4662,16 +4718,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼9</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -4680,17 +4738,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4700,7 +4758,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4709,18 +4767,16 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>▼10</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4738,7 +4794,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -4828,7 +4884,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35,230원</t>
+          <t>35,124원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4838,11 +4894,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>▼81원</t>
+          <t>▼187원</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -4853,7 +4909,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4877,7 +4933,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>20,233원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4891,7 +4947,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -4900,7 +4956,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4909,27 +4965,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>식물성 멜라토닌 함유 멜라메이트 구미/로우슈가 구미 (20/50구미)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4938,16 +4994,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>3.67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▲6</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4985,7 +5043,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -4994,7 +5052,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5018,7 +5076,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27,706원</t>
+          <t>27,495원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5032,7 +5090,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5.07</v>
+        <v>4.76</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -5041,7 +5099,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -5050,47 +5108,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>23,420원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>29,006원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼5,586원</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.67</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>▲3</t>
+          <t>▼2</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -5104,42 +5162,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21,325원</t>
+          <t>14,145원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29,006원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>▼7,681원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
+        <v>4.91</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>▼3</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -5195,22 +5251,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>CJ 바이오코어 비피더스 다이어트 유산균 14캡슐 (2주분)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5224,7 +5280,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
@@ -5233,7 +5289,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -5242,22 +5298,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[7월 올영픽] 판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14,960원</t>
+          <t>24,475원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5271,7 +5327,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -5280,7 +5336,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -5289,22 +5345,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[윤광UP]온리추얼 글로우업 글루타치온 콜라겐 7포 (+1포 증정)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14,587원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5318,7 +5374,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.88</v>
+        <v>6</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
@@ -5327,7 +5383,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5341,17 +5397,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미</t>
+          <t>[7월 올영픽] 코자아 식물성 멜라토닌 함유 젤리 기획 (+10구미+틴케이스) (20일분)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>29,500원</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5365,7 +5421,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>6.33</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -5374,7 +5430,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -5383,22 +5439,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24,466원</t>
+          <t>27,166원</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5412,7 +5468,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.67</v>
+        <v>6.5</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -5421,7 +5477,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -5430,22 +5486,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17,057원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5459,7 +5515,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.71</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
@@ -5468,7 +5524,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -5477,22 +5533,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CJ 바이오코어 비피더스 다이어트 유산균 14캡슐 (2주분)</t>
+          <t>[골라담기] 닥터언 매일루틴 이너헬스 8종 택 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>닥터언</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>4,066원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5506,7 +5562,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
@@ -5515,7 +5571,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -5529,17 +5585,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 속쓰헤소제 4포입 3종(플러스,에이,브이)</t>
+          <t>올더베러 웰니스 구미 30일분 6종 택1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15,435원</t>
+          <t>9,966원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5553,7 +5609,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
@@ -5562,7 +5618,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5571,47 +5627,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+          <t>[추성훈PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>17,706원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>▲5,000원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
+        <v>7.67</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>▼16</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -5620,22 +5674,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>온리추얼 리셋 브이라인 7포 (+1포 증정) (8일분)</t>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>17,057원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5649,7 +5703,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>6.71</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
@@ -5658,7 +5712,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -5667,47 +5721,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+          <t>[7월 올영픽] 오니스트 트리플콜라겐 오렌지 14일 루틴</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>오니스트</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9,700원</t>
+          <t>29,233원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10,534원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>▼834원</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>▼8</t>
+          <t>🆕</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -5721,40 +5773,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[7월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포) (14일분)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17,700원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5,742원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲158원</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>▼12</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5830,25 +5884,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="D2" t="n">
         <v>21.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.7</v>
+        <v>-8.4</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -5914,22 +5968,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>6.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4</v>
+        <v>-1.7</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5942,22 +5996,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7</v>
+        <v>-3.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6026,25 +6080,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>26.7</v>
       </c>
       <c r="D9" t="n">
         <v>18.3</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -6054,16 +6108,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3</v>
+        <v>-1.7</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -6072,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -6082,16 +6136,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -6100,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6110,25 +6164,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>38.3</v>
       </c>
       <c r="D12" t="n">
         <v>28.3</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -6168,7 +6222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6230,22 +6284,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>11.7</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6258,19 +6312,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -6286,25 +6340,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -6338,7 +6392,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6350,10 +6404,10 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6362,35 +6416,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
+        <v>3.3</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6399,17 +6449,13 @@
       <c r="C8" t="n">
         <v>3.3</v>
       </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-3</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6418,7 +6464,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6427,12 +6473,8 @@
       <c r="C9" t="n">
         <v>3.3</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -6446,7 +6488,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6455,22 +6497,26 @@
       <c r="C10" t="n">
         <v>3.3</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6479,26 +6525,22 @@
       <c r="C11" t="n">
         <v>3.3</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6508,10 +6550,10 @@
         <v>3.3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6526,35 +6568,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6564,10 +6606,10 @@
         <v>1.7</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -6582,7 +6624,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6591,8 +6633,12 @@
       <c r="C15" t="n">
         <v>1.7</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
@@ -6606,7 +6652,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6622,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -6634,7 +6680,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6646,10 +6692,10 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6658,7 +6704,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>센트룸</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6667,13 +6713,17 @@
       <c r="C18" t="n">
         <v>1.7</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -6682,7 +6732,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6694,10 +6744,10 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -6706,7 +6756,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6715,8 +6765,12 @@
       <c r="C20" t="n">
         <v>1.7</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
@@ -6730,7 +6784,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6740,10 +6794,10 @@
         <v>1.7</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -6758,7 +6812,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6767,26 +6821,22 @@
       <c r="C22" t="n">
         <v>1.7</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6795,8 +6845,12 @@
       <c r="C23" t="n">
         <v>1.7</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
@@ -6810,7 +6864,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>슬리플러스</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6862,7 +6916,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>슬리플러스</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6871,12 +6925,8 @@
       <c r="C26" t="n">
         <v>1.7</v>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
         <v>0</v>
       </c>
@@ -6890,7 +6940,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6899,12 +6949,8 @@
       <c r="C27" t="n">
         <v>1.7</v>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>0</v>
       </c>
@@ -6918,7 +6964,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6970,7 +7016,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6979,8 +7025,12 @@
       <c r="C30" t="n">
         <v>1.7</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
@@ -6994,7 +7044,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7004,10 +7054,10 @@
         <v>1.7</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -7022,7 +7072,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -7040,6 +7090,130 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>닥터언</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스헬퍼</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>오니스트</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/monthly/2026-07_월별취합.xlsx
+++ b/data/monthly/2026-07_월별취합.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기_카드형" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰_카드형" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="6" state="hidden" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영_카드형" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="브랜드통계" sheetId="9" state="visible" r:id="rId9"/>
